--- a/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260818.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00403A/ETF_Investment_Portfolio_20260818.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>16.18%</t>
+          <t>16.45%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>3,515,000</t>
+          <t>1,690,000</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>6.22%</t>
+          <t>6.04%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>欣興</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>1,690,000</t>
+          <t>8,460,000</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.03%</t>
+          <t>5.58%</t>
         </is>
       </c>
     </row>
@@ -682,29 +682,29 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.39%</t>
+          <t>5.42%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>欣興</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>8,460,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.32%</t>
+          <t>5.25%</t>
         </is>
       </c>
     </row>
@@ -726,51 +726,51 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.80%</t>
+          <t>4.72%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>2327</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>國巨*</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>1,060,000</t>
+          <t>9,785,000</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.45%</t>
+          <t>3.25%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2327</t>
+          <t>6223</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>國巨*</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>9,785,000</t>
+          <t>1,060,000</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.34%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -792,95 +792,95 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3653</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>2,307,000</t>
+          <t>1,020,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.97%</t>
+          <t>3.03%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>28,000,000</t>
+          <t>2,307,000</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.86%</t>
+          <t>2.96%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>華邦電</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>8,000,000</t>
+          <t>28,000,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.76%</t>
+          <t>2.85%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>3653</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>8,000,000</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.40%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.25%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.16%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -946,139 +946,139 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.05%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>8046</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>南電</t>
+          <t>大立光</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>2,640,000</t>
+          <t>626,000</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.92%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>8046</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>大立光</t>
+          <t>南電</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>626,000</t>
+          <t>2,640,000</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.89%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>3443</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>環球晶</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>510,000</t>
+          <t>2,800,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.71%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>3443</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>環球晶</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>2,646,000</t>
+          <t>510,000</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.63%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>6274</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>1,680,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3665</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>1,680,000</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.50%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.08%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1205,51 +1205,51 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>610,000</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.57%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>1560</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>中砂</t>
+          <t>聯鈞</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>聯鈞</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>130,000</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -1261,88 +1261,88 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>7769</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>鴻海</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>130,000</t>
+          <t>3,200,000</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>2317</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>鴻海</t>
+          <t>順達</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>3,200,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.44%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>1560</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>旺宏</t>
+          <t>中砂</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>1,050,000</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3211</t>
+          <t>2337</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>順達</t>
+          <t>旺宏</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.42%</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.32%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.21%</t>
+          <t>0.20%</t>
         </is>
       </c>
     </row>
@@ -1415,22 +1415,22 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>4966</t>
+          <t>2059</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>譜瑞-KY</t>
+          <t>川湖</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>500,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.17%</t>
         </is>
       </c>
     </row>
@@ -1459,12 +1459,12 @@
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>臻鼎-KY</t>
+          <t>譜瑞-KY</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -1474,90 +1474,90 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.14%</t>
+          <t>0.16%</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>強茂</t>
+          <t>臻鼎-KY</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>1,500,000</t>
+          <t>500,000</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.14%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>1717</t>
+          <t>2481</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>長興</t>
+          <t>強茂</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>1,500,000</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.12%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>長興</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>700,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.09%</t>
+          <t>0.10%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>2455</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>全新</t>
+          <t>欣銓</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>336,000</t>
+          <t>700,000</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>2455</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>全新</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>350,000</t>
+          <t>200,000</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,22 +1591,22 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>矽力*-KY</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>350,000</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.00%</t>
+          <t>0.05%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>13,709,917,803</t>
+          <t>12,477,282,289</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr"/>
@@ -1747,7 +1747,7 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>-2,100,821,930</t>
+          <t>-352,206,745</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr"/>
